--- a/results/result_evaluation_logs/G_KG_Incorporation_NTT.xlsx
+++ b/results/result_evaluation_logs/G_KG_Incorporation_NTT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,11 +542,6 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Result String</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
         </is>
       </c>
     </row>
@@ -624,11 +619,6 @@
 wd:Q25095540 wd:P175 wd:Q364841 .
 wd:Q25095540 wd:P750 wd:Q1516254 .
 </t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>e28db94f-dea0-44c5-b3e9-83afb2001ab3</t>
         </is>
       </c>
     </row>
@@ -709,11 +699,6 @@
 </t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>bf8cd83e-bcf3-4fca-9e9e-a2c25a44961c</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -791,11 +776,6 @@
 </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>a6216218-4143-4755-a148-044c55dc093c</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -811,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -820,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -829,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -850,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -859,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -925,11 +905,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>cd445221-6c8b-45ee-940a-9acb724e8a5f</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1006,11 +981,6 @@
 </t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>278efc89-639f-4bd6-9563-52608f4dfd2c</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1026,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1035,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1044,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1065,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1074,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1140,11 +1110,6 @@
 </t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>e767529d-0ba6-4e5a-bbbf-278c5ceb717e</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1219,11 +1184,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2226643 wd:P138 wd:Q28937 .
 </t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>b041368d-b355-4424-84e0-9d2c050654c8</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1263,6 @@
 wd:Q2601034 wd:P50 wd:Q2808 .
 wd:Q2601034 wd:P451 wd:Q2601034 .
 </t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>607da486-a5e8-44f1-a1e5-dd54f79d6fa0</t>
         </is>
       </c>
     </row>
@@ -1391,11 +1346,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>e0f5ef72-c176-4e9c-9479-d9c1f139ce0e</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1473,11 +1423,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>36abbe83-2379-4105-94f0-2b39571bfdcd</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1555,11 +1500,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1a0714b2-16c0-4f55-8d24-4aa3cf8ce4c8</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1575,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1584,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1593,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1614,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1623,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1689,11 +1629,6 @@
 </t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>bf73b185-6153-439a-a428-ead9fa447df3</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1709,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1718,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1727,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1748,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1757,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1823,11 +1758,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>a1c241bd-b1b6-45f1-9f8e-2c501b4c0e69</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1843,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1852,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1861,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1882,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1891,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1957,11 +1887,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>149603a2-2ab8-4f19-a9e9-1d07e579a31f</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2036,11 +1961,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q3311362 wd:P361 wd:Q66117 .
 </t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>f7bd2e23-bd26-455e-a645-3538a584a851</t>
         </is>
       </c>
     </row>
@@ -2118,11 +2038,6 @@
 wd:Q7044514 wd:P175 wd:Q234199 .
 wd:Q7044514 wd:P31 wd:Q46046 .
 </t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6f199169-f74f-440f-b7b7-e4a26e098e22</t>
         </is>
       </c>
     </row>
@@ -2201,11 +2116,6 @@
 wd:Q607380 wd:P5588 wd:Q782 .
 wd:Q607380 wd:P186 wd:Q6933370 .
 </t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2bab644f-449e-4e82-adba-d12b24cdb67c</t>
         </is>
       </c>
     </row>
@@ -2290,11 +2200,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>8071de74-2de5-4215-a9cd-d054da8a0e2e</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2371,11 +2276,6 @@
 </t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>32a0e562-fd89-4ff0-bb3c-0f0038273434</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2391,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2400,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2409,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2430,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2439,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2505,11 +2405,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>0c97bf49-77cb-49f6-a503-1de9f47a1e3d</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2585,11 +2480,6 @@
 wd:Q17052475 wd:P31 wd:Q11348 .
 wd:Q17052475 wd:P361 wd:Q395 .
 </t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>1158c8a2-3319-4975-892a-e21bb7554efc</t>
         </is>
       </c>
     </row>
@@ -2671,11 +2561,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>d9edea2e-0177-4eb5-91fc-1ca938faed75</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2753,11 +2638,6 @@
 </t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>e6755a27-ac35-4842-a1b1-2955db7b58c8</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2773,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2782,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2791,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2812,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2821,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2887,11 +2767,6 @@
 </t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2a215116-cf2a-422e-9a96-9680b8b71895</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2979,11 +2854,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>b85a32cc-ebaf-43ac-b104-0629196640e9</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2999,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3008,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3017,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3038,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -3047,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3113,11 +2983,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>85fa540d-6663-4e8b-ba8b-407e21b4b40e</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3163,10 +3028,10 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
@@ -3196,11 +3061,6 @@
 </t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>2ebb5c62-6e99-4fd1-b56e-b1e5f7bedc91</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3216,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -3225,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -3234,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3255,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -3264,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -3330,11 +3190,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>bbdd090c-b71b-4f52-8db6-302ea6b54b7c</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3380,10 +3235,10 @@
         <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
         <v>3</v>
@@ -3411,11 +3266,6 @@
 wd:Q1840968 wd:P361 wd:Q54153 .
 wd:Q8083051 wd:P131 wd:Q36 .
 </t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>c7a5b09c-f3c8-48e2-8dfd-ecdcc5bfe201</t>
         </is>
       </c>
     </row>
@@ -3497,11 +3347,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>7ec12fff-4591-4f05-82c0-24279b363abb</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3579,11 +3424,6 @@
 </t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>27bab644-50a4-4851-a095-b4651543ce7b</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3629,10 +3469,10 @@
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>4</v>
@@ -3663,11 +3503,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>23a4973f-5553-41d9-8405-acec0271a410</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3745,11 +3580,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>229ad11b-4c70-44de-bc4d-24286fa14c35</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3827,11 +3657,6 @@
 </t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>de6bc952-2623-4e4d-a39e-9c74cad1b91b</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3906,11 +3731,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q1490434 wd:P31 wd:Q41298 .
 </t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>0ee8b047-ce3b-47f0-b178-d88a83c03dce</t>
         </is>
       </c>
     </row>
@@ -3991,11 +3811,6 @@
 </t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3587ae3a-a17c-4eed-b757-5e3d62918e0a</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4041,10 +3856,10 @@
         <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
         <v>4</v>
@@ -4075,11 +3890,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>77a2cde2-18d1-42db-9f57-bb065306cc46</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4158,11 +3968,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>f0cb5def-587e-49a1-9d57-d52639cc9b72</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4241,11 +4046,6 @@
 </t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>fd516081-d952-4172-b7c2-bbc97705f098</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4323,11 +4123,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>30d4beab-3e5f-431f-9a2d-708445c47eff</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4373,10 +4168,10 @@
         <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
@@ -4410,11 +4205,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>13382fdd-b915-4151-b322-561b89c4b47e</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4492,11 +4282,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>7c697829-7fab-4d08-9e78-6abd0a1dd113</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4512,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4521,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4530,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4551,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4560,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4626,11 +4411,6 @@
 </t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>ac3951e0-b1eb-432e-8095-0b0fb91dddfa</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4646,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4655,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4664,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4685,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4694,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4760,11 +4540,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>c567a38c-8917-4c0c-8907-db18b5eac99d</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4843,11 +4618,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>aba56bc5-cb32-41f0-aee3-82dbcc947b0d</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4922,11 +4692,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q18036732 wd:P276 wd:Q753805 .
 </t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>ab676202-d6a3-4c71-93eb-939a85740fa3</t>
         </is>
       </c>
     </row>
@@ -5005,11 +4770,6 @@
 wd:Q977911 wd:P131 wd:Q112686 .
 wd:Q979352 wd:P131 wd:Q112686 .
 </t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>b0c48976-cbce-4f65-b939-99939607e0eb</t>
         </is>
       </c>
     </row>
@@ -5091,11 +4851,6 @@
 </t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>3429af31-1fcf-4f7e-82aa-df3418fe7a7d</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5174,11 +4929,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>2d314602-8ebd-486a-a938-440c4acf0afe</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5253,11 +5003,6 @@
 @prefix wd: &lt;http://www.wikidata.org/entity/&gt; .
 wd:Q2362697 wd:P556 wd:Q503601 .
 </t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>b424acd9-cf4f-49e4-b54f-4628c95675f0</t>
         </is>
       </c>
     </row>
